--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jul-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jul-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jul-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jul-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10439,7 +10439,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11537,7 +11537,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jul-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jul-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M183"/>
+  <dimension ref="A1:M187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -623,7 +623,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1200,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1265,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1452,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1517,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1582,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1830,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1956,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2021,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2147,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2334,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2283,7 +2351,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5416-720-CM25</t>
+          <t>5839-97-CC25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2308,37 +2376,41 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.102.016-3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2932.11</v>
+        <v>29792.33</v>
       </c>
     </row>
     <row r="32">
@@ -2392,7 +2464,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2529,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2594,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2588,7 +2672,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2389-396-CM25</t>
+          <t>5413-703-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2608,32 +2692,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,7 +2727,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>15654.65</v>
+        <v>2416.68</v>
       </c>
     </row>
     <row r="37">
@@ -2697,7 +2781,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2710,7 +2798,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2778-574-CM25</t>
+          <t>5839-96-CC25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2730,48 +2818,52 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>61.102.016-3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5597.76</v>
+        <v>19951.66</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2345-423-CM25</t>
+          <t>5416-720-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2796,43 +2888,47 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>70593.19</v>
+        <v>2932.11</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5413-703-CM25</t>
+          <t>2778-574-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2852,48 +2948,52 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2416.68</v>
+        <v>5597.76</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5769-146-CM25</t>
+          <t>2345-423-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +3008,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +3018,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +3033,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +3048,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2548.98</v>
+        <v>70593.19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2852-568-CM25</t>
+          <t>2389-396-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,37 +3069,37 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,7 +3109,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>4875.13</v>
+        <v>15654.65</v>
       </c>
     </row>
     <row r="43">
@@ -3063,7 +3163,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3076,7 +3180,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1224957-762-CM25</t>
+          <t>5178-3164-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3096,17 +3200,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>70.932.800-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,28 +3220,32 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2932.11</v>
+        <v>3122.19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5178-3164-CM25</t>
+          <t>2852-568-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3162,27 +3270,27 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.596.570-5</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3300,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3122.19</v>
+        <v>4875.13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1214102-1249-CM25</t>
+          <t>5769-146-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3218,17 +3326,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>70.835.200-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE PUDAHUEL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,28 +3346,32 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>12435.95</v>
+        <v>2548.98</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4171-481-CM25</t>
+          <t>1214102-1249-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3284,37 +3396,41 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>70.834.500-8</t>
+          <t>70.835.200-4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>4104.98</v>
+        <v>12435.95</v>
       </c>
     </row>
     <row r="48">
@@ -3368,7 +3484,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3381,7 +3501,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1219102-43-CM25</t>
+          <t>4171-481-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3401,48 +3521,52 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>62.000.930-k</t>
+          <t>70.834.500-8</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Defensoría del Contribuyente</t>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>7419.55</v>
+        <v>4104.98</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5586-1991-CM25</t>
+          <t>1224957-762-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3581,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,43 +3591,47 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>70.932.800-K</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>13719.36</v>
+        <v>2932.11</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3560-292-CM25</t>
+          <t>1219102-43-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,53 +3646,57 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>62.000.930-k</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>Defensoría del Contribuyente</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>3232.04</v>
+        <v>7419.55</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>584146-331-CM25</t>
+          <t>1077195-26-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3589,43 +3721,47 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>82.983.100-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>8212.110000000001</v>
+        <v>7593.39</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>889473-1346-CM25</t>
+          <t>2863-46-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3645,22 +3781,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>69.210.400-5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>I MUNICIPALIDAD PUERTO OCTAY</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3673,20 +3809,24 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>52240.64</v>
+        <v>4557.64</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>507428-3224-CM25</t>
+          <t>1233619-548-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3711,32 +3851,32 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.980.930-0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3745,13 +3885,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>401388.19</v>
+        <v>11042.72</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2294-1477-CM25</t>
+          <t>5485-485-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3771,42 +3911,46 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>7113.46</v>
+        <v>2520.42</v>
       </c>
     </row>
     <row r="56">
@@ -3873,7 +4017,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5485-485-CM25</t>
+          <t>507428-3224-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3898,43 +4042,47 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2520.42</v>
+        <v>401388.19</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1233619-548-CM25</t>
+          <t>2294-1477-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3954,17 +4102,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.980.930-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3974,28 +4122,32 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>11042.72</v>
+        <v>7113.46</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2863-46-CM25</t>
+          <t>889473-1346-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4015,22 +4167,22 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.210.400-5</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PUERTO OCTAY</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4043,20 +4195,24 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>4557.64</v>
+        <v>52240.64</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1077195-26-CM25</t>
+          <t>5586-1991-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4081,43 +4237,47 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>82.983.100-7</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Comisión Chilena de Energía Nuclear</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>7593.39</v>
+        <v>13719.36</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4112-145-CM25</t>
+          <t>584146-331-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4137,48 +4297,52 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.181.000-3</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>17057.46</v>
+        <v>8212.110000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>757-348-CM25</t>
+          <t>3560-292-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4193,53 +4357,57 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.601.000-k</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>9835.35</v>
+        <v>3232.04</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1233613-1069-CM25</t>
+          <t>4112-145-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4254,7 +4422,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4264,43 +4432,47 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>69.181.000-3</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>11925.56</v>
+        <v>17057.46</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2778-606-CM25</t>
+          <t>2292-900-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4325,37 +4497,41 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>12355.06</v>
+        <v>36240.62</v>
       </c>
     </row>
     <row r="65">
@@ -4409,7 +4585,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4470,7 +4650,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4483,7 +4667,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2292-900-CM25</t>
+          <t>542429-50-CC25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4503,48 +4687,52 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.979.490-7</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>36240.62</v>
+        <v>17220.19</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1348798-34-CM25</t>
+          <t>2778-606-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4559,37 +4747,37 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>60.910.047-8</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4599,13 +4787,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>24990</v>
+        <v>12355.06</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4858-527-CM25</t>
+          <t>1233613-1069-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4620,37 +4808,37 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.160.700-3</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4660,13 +4848,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>21027.2</v>
+        <v>11925.56</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5586-2014-CM25</t>
+          <t>757-348-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4681,53 +4869,57 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>61.601.000-k</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3721.55</v>
+        <v>9835.35</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1057062-264-CM25</t>
+          <t>542429-49-CC25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4742,7 +4934,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4752,43 +4944,47 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>61.979.490-7</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>8584.66</v>
+        <v>12617.57</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3917-213-CM25</t>
+          <t>1057062-264-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4813,43 +5009,47 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>27274.8</v>
+        <v>8584.66</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2409-831-CM25</t>
+          <t>5586-2014-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4864,7 +5064,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4874,43 +5074,47 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>35918.38</v>
+        <v>3721.55</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3664-154-CM25</t>
+          <t>3917-213-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4925,53 +5129,57 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.081.300-9</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE REQUINOA</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>4274.35</v>
+        <v>27274.8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2377-162-CM25</t>
+          <t>1348798-34-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4986,7 +5194,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4996,12 +5204,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.070.700-4</t>
+          <t>60.910.047-8</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
+          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5011,28 +5219,32 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5096.27</v>
+        <v>24990</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5178-3259-CM25</t>
+          <t>4858-527-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5047,53 +5259,57 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2463.09</v>
+        <v>21027.2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2294-1529-CM25</t>
+          <t>2401-584-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5118,27 +5334,27 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.080.100-0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE RANCAGUA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5148,13 +5364,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>5568.83</v>
+        <v>60706.37</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4388-109-CM25</t>
+          <t>4856-335-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5179,43 +5395,47 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>60.511.000-2</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>44518.85</v>
+        <v>4782.75</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4856-335-CM25</t>
+          <t>4388-109-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5240,43 +5460,47 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.160.700-3</t>
+          <t>60.511.000-2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
+          <t>76.128.275-1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>4782.75</v>
+        <v>44518.85</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2401-584-CM25</t>
+          <t>2294-1529-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5301,43 +5525,47 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.080.100-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>60706.37</v>
+        <v>5568.83</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3882-220-CM25</t>
+          <t>3664-154-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5352,53 +5580,57 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>69.081.300-9</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>I MUNICIPALIDAD DE REQUINOA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3617.55</v>
+        <v>4274.35</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>921831-266-CM25</t>
+          <t>2377-162-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5413,7 +5645,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5423,43 +5655,47 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.980.700-6</t>
+          <t>69.070.700-4</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>5642.12</v>
+        <v>5096.27</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3888-371-CM25</t>
+          <t>2409-831-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5474,7 +5710,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5484,43 +5720,47 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.251.800-4</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>7261.73</v>
+        <v>35918.38</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1233600-552-CM25</t>
+          <t>5178-3259-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5535,7 +5775,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5545,12 +5785,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>70.931.100-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE RENCA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5560,22 +5800,26 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>60128.92</v>
+        <v>2463.09</v>
       </c>
     </row>
     <row r="85">
@@ -5642,7 +5886,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5251-1115-CM25</t>
+          <t>3882-220-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5667,27 +5911,27 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>70.729.100-1</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5697,13 +5941,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>9400.52</v>
+        <v>3617.55</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1417913-157-CM25</t>
+          <t>3888-371-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5723,48 +5967,52 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>70.938.800-2</t>
+          <t>69.251.800-4</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>7565.71</v>
+        <v>7261.73</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1224957-765-CM25</t>
+          <t>1233600-552-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5789,12 +6037,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>70.932.800-K</t>
+          <t>70.931.100-K</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
+          <t>CORP MUNICIPAL DE RENCA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5804,28 +6052,32 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>4563.59</v>
+        <v>60128.92</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1224957-764-CM25</t>
+          <t>3352-203-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5850,27 +6102,27 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>70.932.800-K</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.596.570-5</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5880,13 +6132,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>8960.379999999999</v>
+        <v>3534.24</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5251-1113-CM25</t>
+          <t>921831-266-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5911,43 +6163,47 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>70.729.100-1</t>
+          <t>61.980.700-6</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>5469.17</v>
+        <v>5642.12</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3352-203-CM25</t>
+          <t>1224957-765-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5972,43 +6228,47 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>70.932.800-K</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>3534.24</v>
+        <v>4563.59</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4280-468-CM25</t>
+          <t>5251-1113-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6023,53 +6283,57 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>69.050.900-8</t>
+          <t>70.729.100-1</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CATEMU</t>
+          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>11480.76</v>
+        <v>5469.17</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4556-97-CM25</t>
+          <t>1417913-157-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6084,53 +6348,57 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
+          <t>76.128.275-1</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>6901.76</v>
+        <v>7565.71</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>980313-165-CM25</t>
+          <t>1224957-764-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6145,53 +6413,57 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.250.900-5</t>
+          <t>70.932.800-K</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTUCO</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3130.41</v>
+        <v>8960.379999999999</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>586-309-CM25</t>
+          <t>5251-1115-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6206,7 +6478,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6216,27 +6488,27 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>70.729.100-1</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6246,13 +6518,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>7682.64</v>
+        <v>9400.52</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4020-809-CM25</t>
+          <t>980313-165-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6272,17 +6544,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>69.250.900-5</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>I MUNICIPALIDAD DE ANTUCO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6300,20 +6572,24 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2229.82</v>
+        <v>3130.41</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1233615-1085-CM25</t>
+          <t>586-309-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6328,7 +6604,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6338,27 +6614,27 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6372,13 +6648,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>132268.08</v>
+        <v>7682.64</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5684-365-CM25</t>
+          <t>4020-809-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6393,7 +6669,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6403,43 +6679,47 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>4277.86</v>
+        <v>2229.82</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1230848-159-CM25</t>
+          <t>4556-97-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6454,53 +6734,57 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Calama</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>36125.51</v>
+        <v>6901.76</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2311-3035-CM25</t>
+          <t>4280-468-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6515,53 +6799,57 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>69.110.100-2</t>
+          <t>69.050.900-8</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
+          <t>I MUNICIPALIDAD DE CATEMU</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>21840.55</v>
+        <v>11480.76</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>4454-600-CM25</t>
+          <t>1230848-159-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6576,53 +6864,57 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.150.600-2</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUALQUI</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2497.22</v>
+        <v>36125.51</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1035206-105-CM25</t>
+          <t>1233615-1085-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6637,7 +6929,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6647,43 +6939,47 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>65.165.411-4</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>14831.57</v>
+        <v>132268.08</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5584-88-CM25</t>
+          <t>5684-365-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6698,7 +6994,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6723,12 +7019,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6738,13 +7034,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2567.72</v>
+        <v>4277.86</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>4769-85-CM25</t>
+          <t>2311-3035-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6764,48 +7060,52 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>69.091.400-K</t>
+          <t>69.110.100-2</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA ESTRELLA</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2733</v>
+        <v>21840.55</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>4171-513-CM25</t>
+          <t>4454-600-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6830,43 +7130,47 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>70.834.500-8</t>
+          <t>69.150.600-2</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+          <t>I MUNICIPALIDAD DE HUALQUI</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>3705.42</v>
+        <v>2497.22</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1181235-2-CM25</t>
+          <t>1035206-105-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6891,43 +7195,47 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>65.165.411-4</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE VALPARAISO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>46697.58</v>
+        <v>14831.57</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1110404-891-CM25</t>
+          <t>5584-88-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6952,43 +7260,47 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>8958.92</v>
+        <v>2567.72</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>188-676-CM25</t>
+          <t>4769-85-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7003,7 +7315,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7013,43 +7325,47 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>69.091.400-K</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>I MUNICIPALIDAD DE LA ESTRELLA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>24578.26</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>539119-4438-CM25</t>
+          <t>4171-513-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7064,53 +7380,57 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>70.834.500-8</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2415.7</v>
+        <v>3705.42</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1348798-40-CM25</t>
+          <t>1181235-2-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7125,7 +7445,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7135,43 +7455,47 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>60.910.047-8</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>9475.26</v>
+        <v>46697.58</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3858-284-CM25</t>
+          <t>1110404-891-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7186,47 +7510,51 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>17017</v>
+        <v>8958.92</v>
       </c>
     </row>
     <row r="112">
@@ -7280,7 +7608,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7293,7 +7625,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2577-56-CM25</t>
+          <t>3858-284-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7313,48 +7645,52 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>23875.09</v>
+        <v>17017</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4055-388-CM25</t>
+          <t>4928-60-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7374,48 +7710,52 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>69.150.900-1</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUMBEL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>9003.540000000001</v>
+        <v>10802.82</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1293138-196-CM25</t>
+          <t>539119-4438-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7440,12 +7780,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7455,28 +7795,32 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>19950.23</v>
+        <v>2415.7</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1432083-887-CM25</t>
+          <t>2577-56-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7501,43 +7845,47 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3075.56</v>
+        <v>23875.09</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>4928-60-CM25</t>
+          <t>1348798-40-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7562,12 +7910,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>60.910.047-8</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7577,28 +7925,32 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr"/>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>10802.82</v>
+        <v>9475.26</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2778-635-CM25</t>
+          <t>188-676-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7623,43 +7975,47 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>14244.3</v>
+        <v>24578.26</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1417913-174-CM25</t>
+          <t>2778-635-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7679,48 +8035,52 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>70.938.800-2</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>30565.51</v>
+        <v>14244.3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2380-1430-CM25</t>
+          <t>1293138-196-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7740,48 +8100,52 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr"/>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2809.52</v>
+        <v>19950.23</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2380-1348-CM25</t>
+          <t>1432083-887-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7801,48 +8165,52 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>10899.07</v>
+        <v>3075.56</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2780-291-CM25</t>
+          <t>1417913-174-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7857,7 +8225,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7867,43 +8235,47 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>5322.87</v>
+        <v>30565.51</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>752-315-CM25</t>
+          <t>2380-1430-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7918,7 +8290,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7928,43 +8300,47 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr"/>
+          <t>76.128.275-1</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>3273.33</v>
+        <v>2809.52</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1211839-7476-CM25</t>
+          <t>2380-1348-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7979,53 +8355,57 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>70.856.400-1</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr"/>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>33366.99</v>
+        <v>10899.07</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2793-665-CM25</t>
+          <t>4055-388-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8040,7 +8420,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8050,43 +8430,47 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>69.150.900-1</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>I MUNICIPALIDAD DE YUMBEL</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>4919.22</v>
+        <v>9003.540000000001</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2793-663-CM25</t>
+          <t>2780-291-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8106,48 +8490,52 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>4971.82</v>
+        <v>5322.87</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3134-251-CM25</t>
+          <t>752-315-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8167,48 +8555,52 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>21157.96</v>
+        <v>3273.33</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3712-679-CM25</t>
+          <t>1211839-7476-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8233,27 +8625,27 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.856.400-1</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8263,13 +8655,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>5617.75</v>
+        <v>33366.99</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3416-334-CM25</t>
+          <t>2793-665-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8289,17 +8681,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.101.017-6</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8309,28 +8701,32 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>24150.69</v>
+        <v>4919.22</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>4083-406-CM25</t>
+          <t>2793-663-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8345,7 +8741,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8355,43 +8751,47 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>69.151.002-6</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>10627.89</v>
+        <v>4971.82</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>5490-58-CM25</t>
+          <t>3712-679-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8406,7 +8806,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8416,43 +8816,47 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>24257.83</v>
+        <v>5617.75</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4079-460-CM25</t>
+          <t>3416-334-CM25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8467,7 +8871,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8477,27 +8881,27 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>69.151.000-k</t>
+          <t>61.101.017-6</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8507,13 +8911,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>3885.74</v>
+        <v>24150.69</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3305-433-CM25</t>
+          <t>3134-251-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8528,47 +8932,51 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>69.141.801-4</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TUCAPEL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>4417.09</v>
+        <v>21157.96</v>
       </c>
     </row>
     <row r="134">
@@ -8622,7 +9030,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8635,7 +9047,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1237328-241-CM25</t>
+          <t>4083-406-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8655,32 +9067,32 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>69.151.002-6</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8690,13 +9102,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>11134.85</v>
+        <v>10627.89</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1057931-37-CM25</t>
+          <t>1237328-241-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8721,43 +9133,47 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>8829.799999999999</v>
+        <v>11134.85</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5148-104-CM25</t>
+          <t>4079-460-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8782,43 +9198,47 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.151.000-k</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>4472.02</v>
+        <v>3885.74</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2409-929-CM25</t>
+          <t>3305-433-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8843,12 +9263,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.141.801-4</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE TUCAPEL</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8858,28 +9278,32 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr"/>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>18641.23</v>
+        <v>4417.09</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4371-119-CM25</t>
+          <t>5490-58-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8899,32 +9323,32 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8934,13 +9358,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>3015.22</v>
+        <v>24257.83</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1057299-1070-CM25</t>
+          <t>4371-119-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8965,43 +9389,47 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69.130.601-1</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2374.05</v>
+        <v>3015.22</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2306-802-CM25</t>
+          <t>1057299-1070-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9021,48 +9449,52 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.130.601-1</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>11758.63</v>
+        <v>2374.05</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>624-202-CM25</t>
+          <t>2306-802-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9077,7 +9509,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9087,17 +9519,17 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9110,20 +9542,24 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>6379.26</v>
+        <v>11758.63</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>867990-773-CM25</t>
+          <t>2409-929-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9138,53 +9574,57 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>6436.35</v>
+        <v>18641.23</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>705829-58-CM25</t>
+          <t>5148-104-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9199,7 +9639,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9209,12 +9649,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9224,28 +9664,32 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>5698.73</v>
+        <v>4472.02</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>5839-104-CM25</t>
+          <t>1057931-37-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9260,53 +9704,57 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.102.016-3</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr"/>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>54090.86</v>
+        <v>8829.799999999999</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>4455-490-CM25</t>
+          <t>624-202-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9331,43 +9779,47 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>5626.08</v>
+        <v>6379.26</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2328-793-CM25</t>
+          <t>867990-773-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9392,43 +9844,47 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>13530.12</v>
+        <v>6436.35</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>705829-57-CM25</t>
+          <t>705829-58-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9476,20 +9932,24 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>6742.54</v>
+        <v>5698.73</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1432083-900-CM25</t>
+          <t>5839-104-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9509,48 +9969,52 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.102.016-3</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>8232.360000000001</v>
+        <v>54090.86</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2833-891-CM25</t>
+          <t>4455-490-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9570,48 +10034,52 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.930.600-7</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>3420.06</v>
+        <v>5626.08</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>5865-87-CM25</t>
+          <t>2328-793-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9631,48 +10099,52 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>15972.78</v>
+        <v>13530.12</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5839-99-CM25</t>
+          <t>654478-410-CM25</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9692,22 +10164,22 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.102.016-3</t>
+          <t>61.980.140-7</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SUBSECRETARIA DE PREVENCION DEL DELITO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9720,20 +10192,24 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>8074.22</v>
+        <v>20290.81</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>654478-410-CM25</t>
+          <t>1432083-905-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9758,43 +10234,47 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.980.140-7</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE PREVENCION DEL DELITO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>20290.81</v>
+        <v>10639.24</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1432083-905-CM25</t>
+          <t>1432083-900-CM25</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9842,20 +10322,24 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>10639.24</v>
+        <v>8232.360000000001</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>707423-100-CM25</t>
+          <t>2833-891-CM25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9870,27 +10354,27 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.930.600-7</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9903,20 +10387,24 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>2182.22</v>
+        <v>3420.06</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3858-297-CM25</t>
+          <t>5865-87-CM25</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9931,7 +10419,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9941,43 +10429,47 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>24273.5</v>
+        <v>15972.78</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1339163-45-CM25</t>
+          <t>5839-99-CM25</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9992,53 +10484,57 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.981.070-8</t>
+          <t>61.102.016-3</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA ROSA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>18022.61</v>
+        <v>8074.22</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>4020-870-CM25</t>
+          <t>705829-57-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10053,53 +10549,57 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3658.29</v>
+        <v>6742.54</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>564953-628-CM25</t>
+          <t>3858-297-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10124,43 +10624,47 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>70.902.000-5</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Corporación de Educación y Salud de Las Condes</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>70293.3</v>
+        <v>24273.5</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>4955-81-CM25</t>
+          <t>1339163-45-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10185,12 +10689,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>61.981.070-8</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA ROSA</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10200,12 +10704,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10215,13 +10719,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>6719.81</v>
+        <v>18022.61</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>4955-80-CM25</t>
+          <t>4020-870-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10241,32 +10745,32 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10276,13 +10780,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>11912.95</v>
+        <v>3658.29</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3024-810-CM25</t>
+          <t>707423-100-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10307,43 +10811,47 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>69.130.800-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2697.31</v>
+        <v>2182.22</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2737-497-CM25</t>
+          <t>564953-628-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10358,7 +10866,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10368,43 +10876,47 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>69.050.600-9</t>
+          <t>70.902.000-5</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>4915.18</v>
+        <v>70293.3</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>3082-459-CM25</t>
+          <t>4955-81-CM25</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10419,53 +10931,57 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>69.050.800-1</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANQUEHUE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>3240.7</v>
+        <v>6719.81</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>3486-432-CM25</t>
+          <t>4955-80-CM25</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10480,37 +10996,37 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>69.190.400-8</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10520,13 +11036,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>12194.29</v>
+        <v>11912.95</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>624-206-CM25</t>
+          <t>3024-810-CM25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10541,7 +11057,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10551,43 +11067,47 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>69.130.800-6</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>ATEM INTEGRACION TECNOLOGICA LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>76.086.318-1</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>7125.72</v>
+        <v>2697.31</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>5110-259-CM25</t>
+          <t>2737-497-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10612,43 +11132,47 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>69.050.600-9</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>10675.73</v>
+        <v>4915.18</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2445-3216-CM25</t>
+          <t>3082-459-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10668,48 +11192,52 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.050.800-1</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE PANQUEHUE</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>15214.27</v>
+        <v>3240.7</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3680-213-CM25</t>
+          <t>3486-432-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10734,27 +11262,27 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>69.190.400-8</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10764,13 +11292,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>6668.76</v>
+        <v>12194.29</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>867990-789-CM25</t>
+          <t>624-206-CM25</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10795,27 +11323,27 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>ATEM INTEGRACION TECNOLOGICA LIMITADA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.086.318-1</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10825,13 +11353,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>9531.9</v>
+        <v>7125.72</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2710-666-CM25</t>
+          <t>5110-259-CM25</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10851,48 +11379,52 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>3212.52</v>
+        <v>10675.73</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>4561-91-CM25</t>
+          <t>2445-3216-CM25</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10917,43 +11449,47 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>69.050.200-3</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABILDO</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>7366.1</v>
+        <v>15214.27</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2445-3214-CM25</t>
+          <t>3680-213-CM25</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10973,48 +11509,52 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.051.400-1</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>8770.780000000001</v>
+        <v>6668.76</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1028871-1131-CM25</t>
+          <t>867990-789-CM25</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11029,7 +11569,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -11039,43 +11579,47 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>17009.62</v>
+        <v>9531.9</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1658-3230-CM25</t>
+          <t>2710-666-CM25</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11090,53 +11634,57 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>44904.58</v>
+        <v>3212.52</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1126922-1406-CM25</t>
+          <t>4561-91-CM25</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11151,53 +11699,57 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.050.200-3</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE CABILDO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>4101.79</v>
+        <v>7366.1</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2306-847-CM25</t>
+          <t>2445-3214-CM25</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11212,53 +11764,57 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>7233.77</v>
+        <v>8770.780000000001</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>768-426-CM25</t>
+          <t>1028871-1131-CM25</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11283,27 +11839,27 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>72.223.100-7</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11313,13 +11869,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>4495.52</v>
+        <v>17009.62</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2825-348-CM25</t>
+          <t>1658-3230-CM25</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11344,27 +11900,27 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>ATEM INTEGRACION TECNOLOGICA LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>76.086.318-1</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11374,13 +11930,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>3562.86</v>
+        <v>44904.58</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>4285-144-CM25</t>
+          <t>1126922-1406-CM25</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11405,43 +11961,47 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>7013.76</v>
+        <v>4101.79</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1126922-1457-CM25</t>
+          <t>2306-847-CM25</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11466,12 +12026,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11481,12 +12041,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -11496,13 +12056,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>6625.78</v>
+        <v>7233.77</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>4690-262-CM25</t>
+          <t>768-426-CM25</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11522,48 +12082,52 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>72.223.100-7</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>GOBIERNO REGIONAL DE TARAPACA</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>5846.71</v>
+        <v>4495.52</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1230869-128-CM25</t>
+          <t>2825-348-CM25</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11583,32 +12147,32 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>65.235.450-5</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Corporación Cultural de La Florida</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>ATEM INTEGRACION TECNOLOGICA LIMITADA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.086.318-1</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11618,6 +12182,266 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
+        <v>3562.86</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>4285-144-CM25</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>69.191.000-8</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="n">
+        <v>7013.76</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>1126922-1457-CM25</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>62.000.800-1</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>TIC SERVICES SPA</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="n">
+        <v>6625.78</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>4690-262-CM25</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>69.110.900-3</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MAULE</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="n">
+        <v>5846.71</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>1230869-128-CM25</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>65.235.450-5</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Corporación Cultural de La Florida</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="n">
         <v>2445.45</v>
       </c>
     </row>
